--- a/data/test2/testXlsx2.xlsx
+++ b/data/test2/testXlsx2.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
-    <t>字段名称</t>
+    <t>##字段名称</t>
   </si>
   <si>
     <t>id</t>
@@ -46,7 +46,7 @@
     <t>skill_pool</t>
   </si>
   <si>
-    <t>数据类型</t>
+    <t>##数据类型</t>
   </si>
   <si>
     <t>int</t>
@@ -58,7 +58,7 @@
     <t>(list#sep=|),WeaponType</t>
   </si>
   <si>
-    <t>字段备注</t>
+    <t>##字段备注</t>
   </si>
   <si>
     <t>武器名称</t>
